--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,363 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130794301</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58542</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brammarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>372824</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6247946</v>
+      </c>
+      <c r="S3" t="n">
+        <v>59</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130794299</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brammarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>372824</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6247946</v>
+      </c>
+      <c r="S4" t="n">
+        <v>59</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130794295</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57859</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brammarp, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>372824</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6247946</v>
+      </c>
+      <c r="S5" t="n">
+        <v>59</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>130794301</v>
       </c>
       <c r="B3" t="n">
-        <v>58542</v>
+        <v>58543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>130794299</v>
       </c>
       <c r="B4" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>130794295</v>
       </c>
       <c r="B5" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>130794301</v>
       </c>
       <c r="B3" t="n">
-        <v>58543</v>
+        <v>58544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>130794299</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>130794295</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,224 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131928759</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 2931-2026, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>372826</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6247969</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131928752</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58062</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 2931-2026, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>372826</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6247969</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>131928759</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131928752</v>
       </c>
       <c r="B7" t="n">
-        <v>58062</v>
+        <v>58064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>131928759</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>57906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131928752</v>
       </c>
       <c r="B7" t="n">
-        <v>58064</v>
+        <v>58069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>131928759</v>
       </c>
       <c r="B6" t="n">
-        <v>57906</v>
+        <v>57908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131928752</v>
       </c>
       <c r="B7" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>131928759</v>
       </c>
       <c r="B6" t="n">
-        <v>57908</v>
+        <v>57942</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131928752</v>
       </c>
       <c r="B7" t="n">
-        <v>58071</v>
+        <v>58105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>131928752</v>
       </c>
       <c r="B7" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>131928759</v>
       </c>
       <c r="B6" t="n">
-        <v>57942</v>
+        <v>57943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131928752</v>
       </c>
       <c r="B7" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>131928759</v>
       </c>
       <c r="B6" t="n">
-        <v>57943</v>
+        <v>57947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131928752</v>
       </c>
       <c r="B7" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -675,48 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121810691</v>
+        <v>130794295</v>
       </c>
       <c r="B2" t="n">
-        <v>110850</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221049</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bramarp, 850 m ONO, Småvänderot, Sk</t>
+          <t>Brammarp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372809</v>
+        <v>372824</v>
       </c>
       <c r="R2" t="n">
-        <v>6247949</v>
+        <v>6247946</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,19 +750,24 @@
           <t>Hjärnarp</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M-Äng-0215</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1992-06-22</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1992-06-22</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,35 +778,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Fattigkärr</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130794301</v>
+        <v>131928759</v>
       </c>
       <c r="B3" t="n">
-        <v>58564</v>
+        <v>57969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,49 +805,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brammarp, Sk</t>
+          <t>A 2931-2026, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372824</v>
+        <v>372826</v>
       </c>
       <c r="R3" t="n">
-        <v>6247946</v>
+        <v>6247969</v>
       </c>
       <c r="S3" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,12 +891,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -908,7 +906,7 @@
         <v>130794299</v>
       </c>
       <c r="B4" t="n">
-        <v>58041</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130794295</v>
+        <v>131928752</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>58134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,16 +1033,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,23 +1059,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brammarp, Sk</t>
+          <t>A 2931-2026, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372824</v>
+        <v>372826</v>
       </c>
       <c r="R5" t="n">
-        <v>6247946</v>
+        <v>6247969</v>
       </c>
       <c r="S5" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:24</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1119,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131928759</v>
+        <v>130794301</v>
       </c>
       <c r="B6" t="n">
-        <v>57947</v>
+        <v>58636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,49 +1142,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 2931-2026, Sk</t>
+          <t>Brammarp, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372826</v>
+        <v>372824</v>
       </c>
       <c r="R6" t="n">
-        <v>6247969</v>
+        <v>6247946</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,12 +1208,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,72 +1238,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131928752</v>
+        <v>121810691</v>
       </c>
       <c r="B7" t="n">
-        <v>58112</v>
+        <v>111128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>221049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 2931-2026, Sk</t>
+          <t>Bramarp, 850 m ONO, Småvänderot, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372826</v>
+        <v>372809</v>
       </c>
       <c r="R7" t="n">
-        <v>6247969</v>
+        <v>6247949</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,14 +1313,19 @@
           <t>Hjärnarp</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>M-Äng-0215</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>1992-06-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>1992-06-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,19 +1336,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Fattigkärr</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Mats Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2931-2026 artfynd.xlsx
+++ b/artfynd/A 2931-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130794295</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928759</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130794299</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928752</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130794301</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,8 +1388,21 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121810691</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>